--- a/VerveStacks_VNM/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_VNM/SuppXLS/Scen_Base_VS.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VNM\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88F4ECC5-EAB9-48DF-9536-4BB7DDCE8956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F026AD43-ABE1-4C28-AC45-B7FCAD0343D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Veda" sheetId="1" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="5" r:id="rId2"/>
+    <sheet name="re_targets" sheetId="5" r:id="rId1"/>
+    <sheet name="Veda" sheetId="1" r:id="rId2"/>
     <sheet name="buildrates" sheetId="4" r:id="rId3"/>
     <sheet name="historical_data_long" sheetId="3" r:id="rId4"/>
   </sheets>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="133">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -388,6 +388,9 @@
   </si>
   <si>
     <t>\I: hydro</t>
+  </si>
+  <si>
+    <t>UCE_min oil fleet utilization</t>
   </si>
   <si>
     <t>windoff</t>
@@ -530,8 +533,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -659,7 +663,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -672,6 +676,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="4"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1013,6 +1018,721 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3AA4B7-47FD-4F93-B895-20A45A866818}">
+  <dimension ref="B9:L29"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" t="s">
+        <v>101</v>
+      </c>
+      <c r="L10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B11">
+        <v>2030</v>
+      </c>
+      <c r="C11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11">
+        <v>0.3</v>
+      </c>
+      <c r="F11" t="s">
+        <v>105</v>
+      </c>
+      <c r="G11" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" t="s">
+        <v>107</v>
+      </c>
+      <c r="I11" s="13">
+        <v>45061</v>
+      </c>
+      <c r="J11" t="s">
+        <v>108</v>
+      </c>
+      <c r="K11" t="s">
+        <v>109</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B12">
+        <v>2030</v>
+      </c>
+      <c r="C12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12">
+        <v>16.3</v>
+      </c>
+      <c r="F12" t="s">
+        <v>105</v>
+      </c>
+      <c r="G12" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" t="s">
+        <v>112</v>
+      </c>
+      <c r="I12" s="13">
+        <v>45762</v>
+      </c>
+      <c r="J12" t="s">
+        <v>113</v>
+      </c>
+      <c r="K12" t="s">
+        <v>114</v>
+      </c>
+      <c r="L12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B13">
+        <v>2030</v>
+      </c>
+      <c r="C13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13">
+        <v>2.27</v>
+      </c>
+      <c r="F13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" t="s">
+        <v>106</v>
+      </c>
+      <c r="H13" t="s">
+        <v>107</v>
+      </c>
+      <c r="I13" s="13">
+        <v>45061</v>
+      </c>
+      <c r="J13" t="s">
+        <v>108</v>
+      </c>
+      <c r="K13" t="s">
+        <v>109</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B14">
+        <v>2030</v>
+      </c>
+      <c r="C14" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14">
+        <v>4.8810000000000002</v>
+      </c>
+      <c r="F14" t="s">
+        <v>105</v>
+      </c>
+      <c r="G14" t="s">
+        <v>111</v>
+      </c>
+      <c r="H14" t="s">
+        <v>112</v>
+      </c>
+      <c r="I14" s="13">
+        <v>45762</v>
+      </c>
+      <c r="J14" t="s">
+        <v>113</v>
+      </c>
+      <c r="K14" t="s">
+        <v>114</v>
+      </c>
+      <c r="L14" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B15">
+        <v>2030</v>
+      </c>
+      <c r="C15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15">
+        <v>30.126999999999999</v>
+      </c>
+      <c r="F15" t="s">
+        <v>105</v>
+      </c>
+      <c r="G15" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" t="s">
+        <v>107</v>
+      </c>
+      <c r="I15" s="13">
+        <v>45061</v>
+      </c>
+      <c r="J15" t="s">
+        <v>108</v>
+      </c>
+      <c r="K15" t="s">
+        <v>109</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B16">
+        <v>2030</v>
+      </c>
+      <c r="C16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16">
+        <v>37.33</v>
+      </c>
+      <c r="F16" t="s">
+        <v>105</v>
+      </c>
+      <c r="G16" t="s">
+        <v>106</v>
+      </c>
+      <c r="H16" t="s">
+        <v>107</v>
+      </c>
+      <c r="I16" s="13">
+        <v>45061</v>
+      </c>
+      <c r="J16" t="s">
+        <v>108</v>
+      </c>
+      <c r="K16" t="s">
+        <v>109</v>
+      </c>
+      <c r="L16" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B17">
+        <v>2030</v>
+      </c>
+      <c r="C17" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17">
+        <v>29.346</v>
+      </c>
+      <c r="F17" t="s">
+        <v>105</v>
+      </c>
+      <c r="G17" t="s">
+        <v>106</v>
+      </c>
+      <c r="H17" t="s">
+        <v>107</v>
+      </c>
+      <c r="I17" s="13">
+        <v>45061</v>
+      </c>
+      <c r="J17" t="s">
+        <v>108</v>
+      </c>
+      <c r="K17" t="s">
+        <v>109</v>
+      </c>
+      <c r="L17" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B18">
+        <v>2030</v>
+      </c>
+      <c r="C18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18">
+        <v>34.667000000000002</v>
+      </c>
+      <c r="F18" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" t="s">
+        <v>111</v>
+      </c>
+      <c r="H18" t="s">
+        <v>112</v>
+      </c>
+      <c r="I18" s="13">
+        <v>45762</v>
+      </c>
+      <c r="J18" t="s">
+        <v>113</v>
+      </c>
+      <c r="K18" t="s">
+        <v>114</v>
+      </c>
+      <c r="L18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B19">
+        <v>2030</v>
+      </c>
+      <c r="C19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19">
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>105</v>
+      </c>
+      <c r="G19" t="s">
+        <v>106</v>
+      </c>
+      <c r="H19" t="s">
+        <v>107</v>
+      </c>
+      <c r="I19" s="13">
+        <v>45061</v>
+      </c>
+      <c r="J19" t="s">
+        <v>108</v>
+      </c>
+      <c r="K19" t="s">
+        <v>109</v>
+      </c>
+      <c r="L19" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B20">
+        <v>2030</v>
+      </c>
+      <c r="C20" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20">
+        <v>17.032</v>
+      </c>
+      <c r="F20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G20" t="s">
+        <v>111</v>
+      </c>
+      <c r="H20" t="s">
+        <v>112</v>
+      </c>
+      <c r="I20" s="13">
+        <v>45762</v>
+      </c>
+      <c r="J20" t="s">
+        <v>113</v>
+      </c>
+      <c r="K20" t="s">
+        <v>114</v>
+      </c>
+      <c r="L20" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B21">
+        <v>2030</v>
+      </c>
+      <c r="C21" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21">
+        <v>21.88</v>
+      </c>
+      <c r="F21" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" t="s">
+        <v>106</v>
+      </c>
+      <c r="H21" t="s">
+        <v>107</v>
+      </c>
+      <c r="I21" s="13">
+        <v>45061</v>
+      </c>
+      <c r="J21" t="s">
+        <v>108</v>
+      </c>
+      <c r="K21" t="s">
+        <v>109</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B22">
+        <v>2030</v>
+      </c>
+      <c r="C22" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22">
+        <v>38.029000000000003</v>
+      </c>
+      <c r="F22" t="s">
+        <v>105</v>
+      </c>
+      <c r="G22" t="s">
+        <v>111</v>
+      </c>
+      <c r="H22" t="s">
+        <v>112</v>
+      </c>
+      <c r="I22" s="13">
+        <v>45762</v>
+      </c>
+      <c r="J22" t="s">
+        <v>113</v>
+      </c>
+      <c r="K22" t="s">
+        <v>114</v>
+      </c>
+      <c r="L22" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B23">
+        <v>2030</v>
+      </c>
+      <c r="C23" t="s">
+        <v>122</v>
+      </c>
+      <c r="D23" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23">
+        <v>2.4</v>
+      </c>
+      <c r="F23" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" t="s">
+        <v>106</v>
+      </c>
+      <c r="H23" t="s">
+        <v>107</v>
+      </c>
+      <c r="I23" s="13">
+        <v>45061</v>
+      </c>
+      <c r="J23" t="s">
+        <v>108</v>
+      </c>
+      <c r="K23" t="s">
+        <v>109</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B24">
+        <v>2030</v>
+      </c>
+      <c r="C24" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24" t="s">
+        <v>104</v>
+      </c>
+      <c r="E24">
+        <v>6</v>
+      </c>
+      <c r="F24" t="s">
+        <v>105</v>
+      </c>
+      <c r="G24" t="s">
+        <v>111</v>
+      </c>
+      <c r="H24" t="s">
+        <v>112</v>
+      </c>
+      <c r="I24" s="13">
+        <v>45762</v>
+      </c>
+      <c r="J24" t="s">
+        <v>113</v>
+      </c>
+      <c r="K24" t="s">
+        <v>114</v>
+      </c>
+      <c r="L24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B25">
+        <v>2030</v>
+      </c>
+      <c r="C25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25">
+        <v>22.58</v>
+      </c>
+      <c r="F25" t="s">
+        <v>105</v>
+      </c>
+      <c r="G25" t="s">
+        <v>106</v>
+      </c>
+      <c r="H25" t="s">
+        <v>107</v>
+      </c>
+      <c r="I25" s="13">
+        <v>45061</v>
+      </c>
+      <c r="J25" t="s">
+        <v>108</v>
+      </c>
+      <c r="K25" t="s">
+        <v>109</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B26">
+        <v>2030</v>
+      </c>
+      <c r="C26" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26">
+        <v>73.415999999999997</v>
+      </c>
+      <c r="F26" t="s">
+        <v>105</v>
+      </c>
+      <c r="G26" t="s">
+        <v>111</v>
+      </c>
+      <c r="H26" t="s">
+        <v>112</v>
+      </c>
+      <c r="I26" s="13">
+        <v>45762</v>
+      </c>
+      <c r="J26" t="s">
+        <v>113</v>
+      </c>
+      <c r="K26" t="s">
+        <v>114</v>
+      </c>
+      <c r="L26" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B27">
+        <v>2030</v>
+      </c>
+      <c r="C27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" t="s">
+        <v>125</v>
+      </c>
+      <c r="E27">
+        <v>567</v>
+      </c>
+      <c r="F27" t="s">
+        <v>105</v>
+      </c>
+      <c r="G27" t="s">
+        <v>106</v>
+      </c>
+      <c r="H27" t="s">
+        <v>107</v>
+      </c>
+      <c r="I27" s="13">
+        <v>45061</v>
+      </c>
+      <c r="J27" t="s">
+        <v>108</v>
+      </c>
+      <c r="K27" t="s">
+        <v>109</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B28">
+        <v>2030</v>
+      </c>
+      <c r="C28" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28">
+        <v>18.8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>105</v>
+      </c>
+      <c r="G28" t="s">
+        <v>106</v>
+      </c>
+      <c r="H28" t="s">
+        <v>107</v>
+      </c>
+      <c r="I28" s="13">
+        <v>45061</v>
+      </c>
+      <c r="J28" t="s">
+        <v>108</v>
+      </c>
+      <c r="K28" t="s">
+        <v>109</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="B29">
+        <v>2030</v>
+      </c>
+      <c r="C29" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" t="s">
+        <v>129</v>
+      </c>
+      <c r="E29">
+        <v>47</v>
+      </c>
+      <c r="F29" t="s">
+        <v>105</v>
+      </c>
+      <c r="G29" t="s">
+        <v>106</v>
+      </c>
+      <c r="H29" t="s">
+        <v>107</v>
+      </c>
+      <c r="I29" s="13">
+        <v>45061</v>
+      </c>
+      <c r="J29" t="s">
+        <v>108</v>
+      </c>
+      <c r="K29" t="s">
+        <v>109</v>
+      </c>
+      <c r="L29" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AL40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -1043,7 +1763,7 @@
     <col min="33" max="33" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="7" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="7.86328125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="5.265625" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="11.19921875" bestFit="1" customWidth="1"/>
   </cols>
@@ -1400,7 +2120,7 @@
     </row>
     <row r="10" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
@@ -1410,10 +2130,34 @@
       <c r="J10" s="3">
         <v>0.31402360435999416</v>
       </c>
+      <c r="AF10" t="s">
+        <v>88</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH10">
+        <f>-1/8.76</f>
+        <v>-0.11415525114155252</v>
+      </c>
+      <c r="AI10" s="2">
+        <f>VLOOKUP(AG10,$F$3:$J$11,2,FALSE)</f>
+        <v>65535</v>
+      </c>
+      <c r="AJ10" s="12">
+        <f>AI10*$AD$1</f>
+        <v>13107</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:38" ht="14.65" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G11" s="3">
         <v>9.2543334663297422E-2</v>
@@ -1741,721 +2485,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6DA95A4-1CB0-41C7-96F4-AC0F64025341}">
-  <dimension ref="B9:L29"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" t="s">
-        <v>94</v>
-      </c>
-      <c r="F10" t="s">
-        <v>95</v>
-      </c>
-      <c r="G10" t="s">
-        <v>96</v>
-      </c>
-      <c r="H10" t="s">
-        <v>97</v>
-      </c>
-      <c r="I10" t="s">
-        <v>98</v>
-      </c>
-      <c r="J10" t="s">
-        <v>99</v>
-      </c>
-      <c r="K10" t="s">
-        <v>100</v>
-      </c>
-      <c r="L10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B11">
-        <v>2030</v>
-      </c>
-      <c r="C11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11">
-        <v>0.3</v>
-      </c>
-      <c r="F11" t="s">
-        <v>104</v>
-      </c>
-      <c r="G11" t="s">
-        <v>105</v>
-      </c>
-      <c r="H11" t="s">
-        <v>106</v>
-      </c>
-      <c r="I11" s="12">
-        <v>45061</v>
-      </c>
-      <c r="J11" t="s">
-        <v>107</v>
-      </c>
-      <c r="K11" t="s">
-        <v>108</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B12">
-        <v>2030</v>
-      </c>
-      <c r="C12" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12">
-        <v>16.3</v>
-      </c>
-      <c r="F12" t="s">
-        <v>104</v>
-      </c>
-      <c r="G12" t="s">
-        <v>110</v>
-      </c>
-      <c r="H12" t="s">
-        <v>111</v>
-      </c>
-      <c r="I12" s="12">
-        <v>45762</v>
-      </c>
-      <c r="J12" t="s">
-        <v>112</v>
-      </c>
-      <c r="K12" t="s">
-        <v>113</v>
-      </c>
-      <c r="L12" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B13">
-        <v>2030</v>
-      </c>
-      <c r="C13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E13">
-        <v>2.27</v>
-      </c>
-      <c r="F13" t="s">
-        <v>104</v>
-      </c>
-      <c r="G13" t="s">
-        <v>105</v>
-      </c>
-      <c r="H13" t="s">
-        <v>106</v>
-      </c>
-      <c r="I13" s="12">
-        <v>45061</v>
-      </c>
-      <c r="J13" t="s">
-        <v>107</v>
-      </c>
-      <c r="K13" t="s">
-        <v>108</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B14">
-        <v>2030</v>
-      </c>
-      <c r="C14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E14">
-        <v>4.8810000000000002</v>
-      </c>
-      <c r="F14" t="s">
-        <v>104</v>
-      </c>
-      <c r="G14" t="s">
-        <v>110</v>
-      </c>
-      <c r="H14" t="s">
-        <v>111</v>
-      </c>
-      <c r="I14" s="12">
-        <v>45762</v>
-      </c>
-      <c r="J14" t="s">
-        <v>112</v>
-      </c>
-      <c r="K14" t="s">
-        <v>113</v>
-      </c>
-      <c r="L14" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B15">
-        <v>2030</v>
-      </c>
-      <c r="C15" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15">
-        <v>30.126999999999999</v>
-      </c>
-      <c r="F15" t="s">
-        <v>104</v>
-      </c>
-      <c r="G15" t="s">
-        <v>105</v>
-      </c>
-      <c r="H15" t="s">
-        <v>106</v>
-      </c>
-      <c r="I15" s="12">
-        <v>45061</v>
-      </c>
-      <c r="J15" t="s">
-        <v>107</v>
-      </c>
-      <c r="K15" t="s">
-        <v>108</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B16">
-        <v>2030</v>
-      </c>
-      <c r="C16" t="s">
-        <v>117</v>
-      </c>
-      <c r="D16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16">
-        <v>37.33</v>
-      </c>
-      <c r="F16" t="s">
-        <v>104</v>
-      </c>
-      <c r="G16" t="s">
-        <v>105</v>
-      </c>
-      <c r="H16" t="s">
-        <v>106</v>
-      </c>
-      <c r="I16" s="12">
-        <v>45061</v>
-      </c>
-      <c r="J16" t="s">
-        <v>107</v>
-      </c>
-      <c r="K16" t="s">
-        <v>108</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B17">
-        <v>2030</v>
-      </c>
-      <c r="C17" t="s">
-        <v>118</v>
-      </c>
-      <c r="D17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17">
-        <v>29.346</v>
-      </c>
-      <c r="F17" t="s">
-        <v>104</v>
-      </c>
-      <c r="G17" t="s">
-        <v>105</v>
-      </c>
-      <c r="H17" t="s">
-        <v>106</v>
-      </c>
-      <c r="I17" s="12">
-        <v>45061</v>
-      </c>
-      <c r="J17" t="s">
-        <v>107</v>
-      </c>
-      <c r="K17" t="s">
-        <v>108</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B18">
-        <v>2030</v>
-      </c>
-      <c r="C18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18">
-        <v>34.667000000000002</v>
-      </c>
-      <c r="F18" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" t="s">
-        <v>110</v>
-      </c>
-      <c r="H18" t="s">
-        <v>111</v>
-      </c>
-      <c r="I18" s="12">
-        <v>45762</v>
-      </c>
-      <c r="J18" t="s">
-        <v>112</v>
-      </c>
-      <c r="K18" t="s">
-        <v>113</v>
-      </c>
-      <c r="L18" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B19">
-        <v>2030</v>
-      </c>
-      <c r="C19" t="s">
-        <v>119</v>
-      </c>
-      <c r="D19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>104</v>
-      </c>
-      <c r="G19" t="s">
-        <v>105</v>
-      </c>
-      <c r="H19" t="s">
-        <v>106</v>
-      </c>
-      <c r="I19" s="12">
-        <v>45061</v>
-      </c>
-      <c r="J19" t="s">
-        <v>107</v>
-      </c>
-      <c r="K19" t="s">
-        <v>108</v>
-      </c>
-      <c r="L19" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B20">
-        <v>2030</v>
-      </c>
-      <c r="C20" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" t="s">
-        <v>103</v>
-      </c>
-      <c r="E20">
-        <v>17.032</v>
-      </c>
-      <c r="F20" t="s">
-        <v>104</v>
-      </c>
-      <c r="G20" t="s">
-        <v>110</v>
-      </c>
-      <c r="H20" t="s">
-        <v>111</v>
-      </c>
-      <c r="I20" s="12">
-        <v>45762</v>
-      </c>
-      <c r="J20" t="s">
-        <v>112</v>
-      </c>
-      <c r="K20" t="s">
-        <v>113</v>
-      </c>
-      <c r="L20" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B21">
-        <v>2030</v>
-      </c>
-      <c r="C21" t="s">
-        <v>120</v>
-      </c>
-      <c r="D21" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21">
-        <v>21.88</v>
-      </c>
-      <c r="F21" t="s">
-        <v>104</v>
-      </c>
-      <c r="G21" t="s">
-        <v>105</v>
-      </c>
-      <c r="H21" t="s">
-        <v>106</v>
-      </c>
-      <c r="I21" s="12">
-        <v>45061</v>
-      </c>
-      <c r="J21" t="s">
-        <v>107</v>
-      </c>
-      <c r="K21" t="s">
-        <v>108</v>
-      </c>
-      <c r="L21" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B22">
-        <v>2030</v>
-      </c>
-      <c r="C22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D22" t="s">
-        <v>103</v>
-      </c>
-      <c r="E22">
-        <v>38.029000000000003</v>
-      </c>
-      <c r="F22" t="s">
-        <v>104</v>
-      </c>
-      <c r="G22" t="s">
-        <v>110</v>
-      </c>
-      <c r="H22" t="s">
-        <v>111</v>
-      </c>
-      <c r="I22" s="12">
-        <v>45762</v>
-      </c>
-      <c r="J22" t="s">
-        <v>112</v>
-      </c>
-      <c r="K22" t="s">
-        <v>113</v>
-      </c>
-      <c r="L22" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B23">
-        <v>2030</v>
-      </c>
-      <c r="C23" t="s">
-        <v>121</v>
-      </c>
-      <c r="D23" t="s">
-        <v>103</v>
-      </c>
-      <c r="E23">
-        <v>2.4</v>
-      </c>
-      <c r="F23" t="s">
-        <v>104</v>
-      </c>
-      <c r="G23" t="s">
-        <v>105</v>
-      </c>
-      <c r="H23" t="s">
-        <v>106</v>
-      </c>
-      <c r="I23" s="12">
-        <v>45061</v>
-      </c>
-      <c r="J23" t="s">
-        <v>107</v>
-      </c>
-      <c r="K23" t="s">
-        <v>108</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B24">
-        <v>2030</v>
-      </c>
-      <c r="C24" t="s">
-        <v>121</v>
-      </c>
-      <c r="D24" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>104</v>
-      </c>
-      <c r="G24" t="s">
-        <v>110</v>
-      </c>
-      <c r="H24" t="s">
-        <v>111</v>
-      </c>
-      <c r="I24" s="12">
-        <v>45762</v>
-      </c>
-      <c r="J24" t="s">
-        <v>112</v>
-      </c>
-      <c r="K24" t="s">
-        <v>113</v>
-      </c>
-      <c r="L24" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B25">
-        <v>2030</v>
-      </c>
-      <c r="C25" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" t="s">
-        <v>103</v>
-      </c>
-      <c r="E25">
-        <v>22.58</v>
-      </c>
-      <c r="F25" t="s">
-        <v>104</v>
-      </c>
-      <c r="G25" t="s">
-        <v>105</v>
-      </c>
-      <c r="H25" t="s">
-        <v>106</v>
-      </c>
-      <c r="I25" s="12">
-        <v>45061</v>
-      </c>
-      <c r="J25" t="s">
-        <v>107</v>
-      </c>
-      <c r="K25" t="s">
-        <v>108</v>
-      </c>
-      <c r="L25" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B26">
-        <v>2030</v>
-      </c>
-      <c r="C26" t="s">
-        <v>122</v>
-      </c>
-      <c r="D26" t="s">
-        <v>103</v>
-      </c>
-      <c r="E26">
-        <v>73.415999999999997</v>
-      </c>
-      <c r="F26" t="s">
-        <v>104</v>
-      </c>
-      <c r="G26" t="s">
-        <v>110</v>
-      </c>
-      <c r="H26" t="s">
-        <v>111</v>
-      </c>
-      <c r="I26" s="12">
-        <v>45762</v>
-      </c>
-      <c r="J26" t="s">
-        <v>112</v>
-      </c>
-      <c r="K26" t="s">
-        <v>113</v>
-      </c>
-      <c r="L26" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B27">
-        <v>2030</v>
-      </c>
-      <c r="C27" t="s">
-        <v>123</v>
-      </c>
-      <c r="D27" t="s">
-        <v>124</v>
-      </c>
-      <c r="E27">
-        <v>567</v>
-      </c>
-      <c r="F27" t="s">
-        <v>104</v>
-      </c>
-      <c r="G27" t="s">
-        <v>105</v>
-      </c>
-      <c r="H27" t="s">
-        <v>106</v>
-      </c>
-      <c r="I27" s="12">
-        <v>45061</v>
-      </c>
-      <c r="J27" t="s">
-        <v>107</v>
-      </c>
-      <c r="K27" t="s">
-        <v>108</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B28">
-        <v>2030</v>
-      </c>
-      <c r="C28" t="s">
-        <v>125</v>
-      </c>
-      <c r="D28" t="s">
-        <v>126</v>
-      </c>
-      <c r="E28">
-        <v>18.8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>104</v>
-      </c>
-      <c r="G28" t="s">
-        <v>105</v>
-      </c>
-      <c r="H28" t="s">
-        <v>106</v>
-      </c>
-      <c r="I28" s="12">
-        <v>45061</v>
-      </c>
-      <c r="J28" t="s">
-        <v>107</v>
-      </c>
-      <c r="K28" t="s">
-        <v>108</v>
-      </c>
-      <c r="L28" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" ht="409.5" x14ac:dyDescent="0.45">
-      <c r="B29">
-        <v>2030</v>
-      </c>
-      <c r="C29" t="s">
-        <v>127</v>
-      </c>
-      <c r="D29" t="s">
-        <v>128</v>
-      </c>
-      <c r="E29">
-        <v>47</v>
-      </c>
-      <c r="F29" t="s">
-        <v>104</v>
-      </c>
-      <c r="G29" t="s">
-        <v>105</v>
-      </c>
-      <c r="H29" t="s">
-        <v>106</v>
-      </c>
-      <c r="I29" s="12">
-        <v>45061</v>
-      </c>
-      <c r="J29" t="s">
-        <v>107</v>
-      </c>
-      <c r="K29" t="s">
-        <v>108</v>
-      </c>
-      <c r="L29" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2478,12 +2507,12 @@
   <sheetData>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
@@ -2512,7 +2541,7 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11">
         <v>8</v>
@@ -5771,7 +5800,7 @@
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A228" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B228">
         <v>2000</v>
@@ -5869,7 +5898,7 @@
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A235" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B235">
         <v>2001</v>
@@ -5967,7 +5996,7 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A242" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B242">
         <v>2002</v>
@@ -6065,7 +6094,7 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A249" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B249">
         <v>2003</v>
@@ -6163,7 +6192,7 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A256" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B256">
         <v>2004</v>
@@ -6261,7 +6290,7 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A263" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B263">
         <v>2005</v>
@@ -6359,7 +6388,7 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A270" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B270">
         <v>2006</v>
@@ -6457,7 +6486,7 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A277" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B277">
         <v>2007</v>
@@ -6555,7 +6584,7 @@
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A284" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B284">
         <v>2008</v>
@@ -6653,7 +6682,7 @@
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A291" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B291">
         <v>2009</v>
@@ -6765,7 +6794,7 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A299" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B299">
         <v>2010</v>
@@ -6877,7 +6906,7 @@
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A307" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B307">
         <v>2011</v>
@@ -6989,7 +7018,7 @@
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A315" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B315">
         <v>2012</v>
@@ -7101,7 +7130,7 @@
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A323" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B323">
         <v>2013</v>
@@ -7213,7 +7242,7 @@
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A331" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B331">
         <v>2014</v>
@@ -7325,7 +7354,7 @@
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A339" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B339">
         <v>2015</v>
@@ -7437,7 +7466,7 @@
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A347" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B347">
         <v>2016</v>
@@ -7549,7 +7578,7 @@
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A355" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B355">
         <v>2017</v>
@@ -7661,7 +7690,7 @@
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A363" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B363">
         <v>2018</v>
@@ -7773,7 +7802,7 @@
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A371" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B371">
         <v>2019</v>
@@ -7885,7 +7914,7 @@
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A379" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B379">
         <v>2020</v>
@@ -7997,7 +8026,7 @@
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A387" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B387">
         <v>2021</v>
@@ -8109,7 +8138,7 @@
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A395" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B395">
         <v>2022</v>
@@ -8221,7 +8250,7 @@
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A403" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B403">
         <v>2023</v>
@@ -8907,7 +8936,7 @@
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B452">
         <v>2018</v>
@@ -8921,7 +8950,7 @@
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B453">
         <v>2019</v>
@@ -8935,7 +8964,7 @@
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B454">
         <v>2020</v>
@@ -8949,7 +8978,7 @@
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B455">
         <v>2021</v>
@@ -8963,7 +8992,7 @@
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B456">
         <v>2022</v>
@@ -8977,7 +9006,7 @@
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B457">
         <v>2023</v>
@@ -8991,7 +9020,7 @@
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B458">
         <v>2024</v>
@@ -9005,7 +9034,7 @@
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B459">
         <v>2011</v>
@@ -9019,7 +9048,7 @@
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B460">
         <v>2012</v>
@@ -9033,7 +9062,7 @@
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B461">
         <v>2013</v>
@@ -9047,7 +9076,7 @@
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B462">
         <v>2014</v>
@@ -9061,7 +9090,7 @@
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B463">
         <v>2015</v>
@@ -9075,7 +9104,7 @@
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A464" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B464">
         <v>2016</v>
@@ -9089,7 +9118,7 @@
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A465" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B465">
         <v>2017</v>
@@ -9103,7 +9132,7 @@
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A466" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B466">
         <v>2008</v>
@@ -9117,7 +9146,7 @@
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A467" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B467">
         <v>2009</v>
@@ -9131,7 +9160,7 @@
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A468" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B468">
         <v>2010</v>
@@ -9145,7 +9174,7 @@
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A469" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B469">
         <v>2008</v>
@@ -9159,7 +9188,7 @@
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A470" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B470">
         <v>2009</v>
@@ -9173,7 +9202,7 @@
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A471" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B471">
         <v>2010</v>
@@ -9187,7 +9216,7 @@
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A472" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B472">
         <v>2011</v>
@@ -9201,7 +9230,7 @@
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A473" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B473">
         <v>2012</v>
@@ -9215,7 +9244,7 @@
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A474" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B474">
         <v>2013</v>
@@ -9229,7 +9258,7 @@
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A475" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B475">
         <v>2014</v>
@@ -9243,7 +9272,7 @@
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A476" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B476">
         <v>2015</v>
@@ -9257,7 +9286,7 @@
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A477" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B477">
         <v>2016</v>
@@ -9271,7 +9300,7 @@
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A478" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B478">
         <v>2017</v>
@@ -9285,7 +9314,7 @@
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A479" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B479">
         <v>2018</v>
@@ -9299,7 +9328,7 @@
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A480" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B480">
         <v>2019</v>
@@ -9313,7 +9342,7 @@
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A481" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B481">
         <v>2020</v>
@@ -9327,7 +9356,7 @@
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A482" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B482">
         <v>2021</v>
@@ -9341,7 +9370,7 @@
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A483" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B483">
         <v>2022</v>
@@ -9355,7 +9384,7 @@
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A484" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B484">
         <v>2018</v>
@@ -9369,7 +9398,7 @@
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A485" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B485">
         <v>2019</v>
@@ -9383,7 +9412,7 @@
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A486" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B486">
         <v>2020</v>
@@ -9397,7 +9426,7 @@
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A487" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B487">
         <v>2021</v>
@@ -9411,7 +9440,7 @@
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A488" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B488">
         <v>2022</v>
@@ -9425,7 +9454,7 @@
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A489" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B489">
         <v>2023</v>
@@ -9439,7 +9468,7 @@
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A490" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B490">
         <v>2024</v>
@@ -9453,7 +9482,7 @@
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A491" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B491">
         <v>2013</v>
@@ -9467,7 +9496,7 @@
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A492" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B492">
         <v>2014</v>
@@ -9481,7 +9510,7 @@
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A493" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B493">
         <v>2015</v>
@@ -9495,7 +9524,7 @@
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A494" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B494">
         <v>2016</v>
@@ -9509,7 +9538,7 @@
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A495" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B495">
         <v>2017</v>
@@ -9523,7 +9552,7 @@
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A496" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B496">
         <v>2013</v>
@@ -9537,7 +9566,7 @@
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A497" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B497">
         <v>2014</v>
@@ -9551,7 +9580,7 @@
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A498" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B498">
         <v>2015</v>
@@ -9565,7 +9594,7 @@
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A499" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B499">
         <v>2016</v>
@@ -9579,7 +9608,7 @@
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A500" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B500">
         <v>2017</v>
@@ -9593,7 +9622,7 @@
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A501" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B501">
         <v>2018</v>
@@ -9607,7 +9636,7 @@
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A502" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B502">
         <v>2019</v>
@@ -9621,7 +9650,7 @@
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A503" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B503">
         <v>2020</v>
@@ -9635,7 +9664,7 @@
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A504" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B504">
         <v>2021</v>
@@ -9649,7 +9678,7 @@
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A505" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B505">
         <v>2022</v>
